--- a/outputs/daily/hr_rankings_2026-09-06_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-09-06_remaining.xlsx
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>62.7</v>
+        <v>63.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -811,7 +811,7 @@
         <v>45.6</v>
       </c>
       <c r="S2" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -821,39 +821,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1019,12 +1015,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>695734</t>
+          <t>665953</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Daylen Lile</t>
+          <t>Andrés Chaparro</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1049,7 +1045,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1068,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>50.3</v>
+        <v>54.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1082,11 +1078,11 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>35.4</v>
+        <v>44.2</v>
       </c>
       <c r="Q3" t="n">
         <v>47.2</v>
@@ -1095,49 +1091,45 @@
         <v>45.6</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U3" t="n">
-        <v>66.40000000000001</v>
+        <v>24.9</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1157,27 +1149,27 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.8% barrel, 15.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.8% barrel, 15.8 HR allowed</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1187,67 +1179,67 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>7.86</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>38.84</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>88.83</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>99.0687</t>
+          <t>101.0261</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.4455</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.1719</t>
+          <t>0.1904</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3347</t>
+          <t>0.3231</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>70.71</t>
+          <t>74.07</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>42.65</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>49.64</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>25.32</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.1885</t>
+          <t>0.1964</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1303,12 +1295,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>686611</t>
+          <t>691781</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dylan Crews</t>
+          <t>Brady House</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1352,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>50.3</v>
+        <v>53.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1366,11 +1358,11 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q4" t="n">
         <v>47.2</v>
@@ -1379,49 +1371,45 @@
         <v>45.6</v>
       </c>
       <c r="S4" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>78</v>
       </c>
       <c r="U4" t="n">
-        <v>14.1</v>
+        <v>59</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1441,22 +1429,22 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/28, 0 HR</t>
+          <t>Contact streak: 9/23 over last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1471,67 +1459,67 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>47.28</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>90.12</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>100.9631</t>
+          <t>101.662</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.3993</t>
+          <t>0.4253</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.1657</t>
+          <t>0.1616</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>0.3204</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.17</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>38.28</t>
+          <t>30.18</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>34.22</t>
+          <t>31.98</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>26.91</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.1447</t>
+          <t>0.1398</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1587,12 +1575,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>691781</t>
+          <t>686611</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brady House</t>
+          <t>Dylan Crews</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1617,7 +1605,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1636,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>49.7</v>
+        <v>52.8</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1650,11 +1638,11 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q5" t="n">
         <v>47.2</v>
@@ -1663,49 +1651,45 @@
         <v>45.6</v>
       </c>
       <c r="S5" t="n">
-        <v>59.8</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
         <v>78</v>
       </c>
       <c r="U5" t="n">
-        <v>59</v>
+        <v>14.1</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1725,22 +1709,22 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Contact streak: 9/23 over last 7 games</t>
+          <t>Last 7 games: 6/28, 0 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1755,67 +1739,67 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>47.28</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.12</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>101.662</t>
+          <t>100.9631</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4253</t>
+          <t>0.3993</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1616</t>
+          <t>0.1657</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3204</t>
+          <t>0.307</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>73.17</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>30.18</t>
+          <t>38.28</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>31.98</t>
+          <t>34.22</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>26.91</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1398</t>
+          <t>0.1447</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -2151,24 +2135,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>694673</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Abimelec Ortiz</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>WSH</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-09-07T02:10:00Z</t>
@@ -2181,17 +2165,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Justin Wrobleski</t>
+          <t>Andrew Alvarez</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>680736</t>
+          <t>674841</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -2200,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>48.9</v>
+        <v>48.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2214,65 +2198,61 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>38.6</v>
+        <v>44.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>47.2</v>
+        <v>22.3</v>
       </c>
       <c r="R7" t="n">
         <v>45.6</v>
       </c>
       <c r="S7" t="n">
-        <v>95.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U7" t="n">
-        <v>1.6</v>
+        <v>55.9</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -2289,27 +2269,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/23, 0 HR</t>
+          <t>Contact streak: 10/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.8% barrel, 15.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.8% barrel, 3.8 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2319,97 +2299,97 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>45.12</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>90.13</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>99.5696</t>
+          <t>101.464</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>0.4315</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>0.1808</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.294</t>
+          <t>0.3233</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>72.55</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>35.13</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>0.165</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>39.82</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>88.83</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.4213</t>
+          <t>0.3507</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1598</t>
+          <t>0.1116</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>28.63</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -2435,24 +2415,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>682928</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Teoscar Hernández</t>
+          <t>CJ Abrams</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>WSH</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-09-07T02:10:00Z</t>
@@ -2465,17 +2445,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Andrew Alvarez</t>
+          <t>Justin Wrobleski</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>674841</t>
+          <t>680736</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2484,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2498,26 +2478,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>44.3</v>
+        <v>38.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>22.3</v>
+        <v>47.2</v>
       </c>
       <c r="R8" t="n">
         <v>45.6</v>
       </c>
       <c r="S8" t="n">
-        <v>86.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>55.9</v>
+        <v>0</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -2531,7 +2511,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -2569,27 +2549,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Contact streak: 10/27 over last 7 games</t>
+          <t>Last 7 games: 3/28, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.8% barrel, 3.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.8% barrel, 15.8 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -2599,97 +2579,97 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>45.12</t>
+          <t>40.46</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>90.13</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>101.464</t>
+          <t>99.8263</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4315</t>
+          <t>0.4171</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1808</t>
+          <t>0.1735</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3233</t>
+          <t>0.3223</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>72.55</t>
+          <t>72.82</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>35.13</t>
+          <t>43.87</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.01</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>0.2145</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>88.83</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.3507</t>
+          <t>0.4213</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1116</t>
+          <t>0.1598</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>28.63</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -2715,12 +2695,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>682928</t>
+          <t>695734</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CJ Abrams</t>
+          <t>Daylen Lile</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2745,7 +2725,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2764,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>48.2</v>
+        <v>48.4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2778,11 +2758,11 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>38.3</v>
+        <v>35.4</v>
       </c>
       <c r="Q9" t="n">
         <v>47.2</v>
@@ -2791,49 +2771,45 @@
         <v>45.6</v>
       </c>
       <c r="S9" t="n">
-        <v>92.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2853,22 +2829,22 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/28, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -2883,67 +2859,67 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>7.86</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>40.46</t>
+          <t>38.84</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>89.33</t>
+          <t>88.83</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>99.8263</t>
+          <t>99.0687</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4171</t>
+          <t>0.4455</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1735</t>
+          <t>0.1719</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3223</t>
+          <t>0.3347</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>72.82</t>
+          <t>70.71</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>43.87</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>29.01</t>
+          <t>33.25</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.2145</t>
+          <t>0.1885</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2999,24 +2975,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>695670</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Harry Ford</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>WSH</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-09-07T02:10:00Z</t>
@@ -3029,17 +3005,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Andrew Alvarez</t>
+          <t>Justin Wrobleski</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>674841</t>
+          <t>680736</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -3048,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>46.1</v>
+        <v>47.3</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3062,26 +3038,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>31.3</v>
+        <v>35.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>22.3</v>
+        <v>47.2</v>
       </c>
       <c r="R10" t="n">
         <v>45.6</v>
       </c>
       <c r="S10" t="n">
-        <v>100</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>78</v>
       </c>
       <c r="U10" t="n">
-        <v>52.1</v>
+        <v>26.4</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -3095,7 +3071,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -3133,12 +3109,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -3148,112 +3124,112 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Contact streak: 10/29 over last 7 games</t>
+          <t>Last 7 games: 4/23, 1 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.8% barrel, 3.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.8% barrel, 15.8 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>37.48</t>
+          <t>35.37</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>86.41</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>98.4142</t>
+          <t>98.424</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.422</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1497</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3293</t>
+          <t>0.2688</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>69.41</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>32.98</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>33.73</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1641</t>
+          <t>0.126</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>88.83</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.3507</t>
+          <t>0.4213</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1116</t>
+          <t>0.1598</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>28.63</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -3279,12 +3255,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3309,7 +3285,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3328,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3342,11 +3318,11 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>41</v>
+        <v>31.3</v>
       </c>
       <c r="Q11" t="n">
         <v>22.3</v>
@@ -3355,13 +3331,13 @@
         <v>45.6</v>
       </c>
       <c r="S11" t="n">
-        <v>94.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T11" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U11" t="n">
-        <v>50.3</v>
+        <v>52.1</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -3375,7 +3351,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -3413,12 +3389,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -3428,12 +3404,12 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Contact streak: 7/21 over last 7 games</t>
+          <t>Contact streak: 10/29 over last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.8% barrel, 3.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.8% barrel, 3.8 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3443,67 +3419,67 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>37.48</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>90.06</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>100.2939</t>
+          <t>98.4142</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4775</t>
+          <t>0.422</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1888</t>
+          <t>0.1497</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3668</t>
+          <t>0.3293</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>70.08</t>
+          <t>69.46</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>36.05</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>27.63</t>
+          <t>33.73</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1734</t>
+          <t>0.1641</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -3559,24 +3535,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>660688</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Keibert Ruiz</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>WSH</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-09-07T02:10:00Z</t>
@@ -3589,17 +3565,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Justin Wrobleski</t>
+          <t>Andrew Alvarez</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>680736</t>
+          <t>674841</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -3608,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>42.9</v>
+        <v>46</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3622,62 +3598,58 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>16.1</v>
+        <v>41</v>
       </c>
       <c r="Q12" t="n">
-        <v>45.5</v>
+        <v>22.3</v>
       </c>
       <c r="R12" t="n">
         <v>45.6</v>
       </c>
       <c r="S12" t="n">
-        <v>71.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>61.7</v>
+        <v>50.3</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3697,12 +3669,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -3712,12 +3684,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Contact streak: 9/22 over last 7 games</t>
+          <t>Contact streak: 7/21 over last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.8% barrel, 15.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.8% barrel, 3.8 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3727,97 +3699,97 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>35.24</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>90.06</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>97.6371</t>
+          <t>100.2939</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3622</t>
+          <t>0.4775</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1087</t>
+          <t>0.1888</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.2863</t>
+          <t>0.3668</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>67.22</t>
+          <t>70.08</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>55.59</t>
+          <t>36.05</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>27.63</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1396</t>
+          <t>0.1734</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>39.82</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>88.83</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.4213</t>
+          <t>0.3507</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1598</t>
+          <t>0.1116</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>28.63</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -4452,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>39.1</v>
+        <v>39.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4466,7 +4438,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -4479,7 +4451,7 @@
         <v>45.6</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
         <v>78</v>
@@ -4489,39 +4461,35 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5532,7 +5500,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nasim Nunez</t>
+          <t>Nasim Nuñez</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5576,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>32</v>
+        <v>32.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5590,7 +5558,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -5603,7 +5571,7 @@
         <v>45.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -5613,39 +5581,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6186,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>62.7</v>
+        <v>63.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6200,7 +6164,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6213,7 +6177,7 @@
         <v>45.6</v>
       </c>
       <c r="S2" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -6223,39 +6187,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6421,12 +6381,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>695734</t>
+          <t>665953</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Daylen Lile</t>
+          <t>Andrés Chaparro</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -6451,7 +6411,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -6470,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>50.3</v>
+        <v>54.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6484,11 +6444,11 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>35.4</v>
+        <v>44.2</v>
       </c>
       <c r="Q3" t="n">
         <v>47.2</v>
@@ -6497,49 +6457,45 @@
         <v>45.6</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U3" t="n">
-        <v>66.40000000000001</v>
+        <v>24.9</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6559,27 +6515,27 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.8% barrel, 15.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.8% barrel, 15.8 HR allowed</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -6589,67 +6545,67 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>7.86</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>38.84</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>88.83</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>99.0687</t>
+          <t>101.0261</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.4455</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.1719</t>
+          <t>0.1904</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3347</t>
+          <t>0.3231</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>70.71</t>
+          <t>74.07</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>42.65</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>49.64</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>25.32</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.1885</t>
+          <t>0.1964</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -6705,12 +6661,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>686611</t>
+          <t>691781</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dylan Crews</t>
+          <t>Brady House</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -6754,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>50.3</v>
+        <v>53.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6768,11 +6724,11 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q4" t="n">
         <v>47.2</v>
@@ -6781,49 +6737,45 @@
         <v>45.6</v>
       </c>
       <c r="S4" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>78</v>
       </c>
       <c r="U4" t="n">
-        <v>14.1</v>
+        <v>59</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6843,22 +6795,22 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/28, 0 HR</t>
+          <t>Contact streak: 9/23 over last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -6873,67 +6825,67 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>47.28</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>90.12</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>100.9631</t>
+          <t>101.662</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.3993</t>
+          <t>0.4253</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.1657</t>
+          <t>0.1616</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>0.3204</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.17</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>38.28</t>
+          <t>30.18</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>34.22</t>
+          <t>31.98</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>26.91</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.1447</t>
+          <t>0.1398</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -6989,12 +6941,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>691781</t>
+          <t>686611</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brady House</t>
+          <t>Dylan Crews</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -7019,7 +6971,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -7038,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>49.7</v>
+        <v>52.8</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7052,11 +7004,11 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q5" t="n">
         <v>47.2</v>
@@ -7065,49 +7017,45 @@
         <v>45.6</v>
       </c>
       <c r="S5" t="n">
-        <v>59.8</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
         <v>78</v>
       </c>
       <c r="U5" t="n">
-        <v>59</v>
+        <v>14.1</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7127,22 +7075,22 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Contact streak: 9/23 over last 7 games</t>
+          <t>Last 7 games: 6/28, 0 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -7157,67 +7105,67 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>47.28</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.12</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>101.662</t>
+          <t>100.9631</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4253</t>
+          <t>0.3993</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1616</t>
+          <t>0.1657</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3204</t>
+          <t>0.307</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>73.17</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>30.18</t>
+          <t>38.28</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>31.98</t>
+          <t>34.22</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>26.91</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1398</t>
+          <t>0.1447</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -7553,24 +7501,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>694673</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Abimelec Ortiz</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>WSH</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-09-07T02:10:00Z</t>
@@ -7583,17 +7531,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Justin Wrobleski</t>
+          <t>Andrew Alvarez</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>680736</t>
+          <t>674841</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -7602,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>48.9</v>
+        <v>48.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7616,65 +7564,61 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>38.6</v>
+        <v>44.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>47.2</v>
+        <v>22.3</v>
       </c>
       <c r="R7" t="n">
         <v>45.6</v>
       </c>
       <c r="S7" t="n">
-        <v>95.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U7" t="n">
-        <v>1.6</v>
+        <v>55.9</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -7691,27 +7635,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/23, 0 HR</t>
+          <t>Contact streak: 10/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.8% barrel, 15.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.8% barrel, 3.8 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -7721,97 +7665,97 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>45.12</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>90.13</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>99.5696</t>
+          <t>101.464</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>0.4315</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>0.1808</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.294</t>
+          <t>0.3233</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>72.55</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>35.13</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>0.165</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>39.82</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>88.83</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.4213</t>
+          <t>0.3507</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1598</t>
+          <t>0.1116</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>28.63</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -7837,24 +7781,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>682928</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Teoscar Hernández</t>
+          <t>CJ Abrams</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>WSH</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-09-07T02:10:00Z</t>
@@ -7867,17 +7811,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Andrew Alvarez</t>
+          <t>Justin Wrobleski</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>674841</t>
+          <t>680736</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -7886,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7900,26 +7844,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>44.3</v>
+        <v>38.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>22.3</v>
+        <v>47.2</v>
       </c>
       <c r="R8" t="n">
         <v>45.6</v>
       </c>
       <c r="S8" t="n">
-        <v>86.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>55.9</v>
+        <v>0</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -7933,7 +7877,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -7971,27 +7915,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Contact streak: 10/27 over last 7 games</t>
+          <t>Last 7 games: 3/28, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.8% barrel, 3.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.8% barrel, 15.8 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -8001,97 +7945,97 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>45.12</t>
+          <t>40.46</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>90.13</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>101.464</t>
+          <t>99.8263</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4315</t>
+          <t>0.4171</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1808</t>
+          <t>0.1735</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3233</t>
+          <t>0.3223</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>72.55</t>
+          <t>72.82</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>35.13</t>
+          <t>43.87</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.01</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>0.2145</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>88.83</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.3507</t>
+          <t>0.4213</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1116</t>
+          <t>0.1598</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>28.63</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -8117,12 +8061,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>682928</t>
+          <t>695734</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CJ Abrams</t>
+          <t>Daylen Lile</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -8147,7 +8091,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -8166,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>48.2</v>
+        <v>48.4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8180,11 +8124,11 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>38.3</v>
+        <v>35.4</v>
       </c>
       <c r="Q9" t="n">
         <v>47.2</v>
@@ -8193,49 +8137,45 @@
         <v>45.6</v>
       </c>
       <c r="S9" t="n">
-        <v>92.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8255,22 +8195,22 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/28, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -8285,67 +8225,67 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>7.86</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>40.46</t>
+          <t>38.84</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>89.33</t>
+          <t>88.83</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>99.8263</t>
+          <t>99.0687</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4171</t>
+          <t>0.4455</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1735</t>
+          <t>0.1719</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3223</t>
+          <t>0.3347</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>72.82</t>
+          <t>70.71</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>43.87</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>29.01</t>
+          <t>33.25</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.2145</t>
+          <t>0.1885</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -8401,24 +8341,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>695670</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Harry Ford</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>WSH</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-09-07T02:10:00Z</t>
@@ -8431,17 +8371,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Andrew Alvarez</t>
+          <t>Justin Wrobleski</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>674841</t>
+          <t>680736</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -8450,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>46.1</v>
+        <v>47.3</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8464,26 +8404,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>31.3</v>
+        <v>35.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>22.3</v>
+        <v>47.2</v>
       </c>
       <c r="R10" t="n">
         <v>45.6</v>
       </c>
       <c r="S10" t="n">
-        <v>100</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>78</v>
       </c>
       <c r="U10" t="n">
-        <v>52.1</v>
+        <v>26.4</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -8497,7 +8437,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -8535,12 +8475,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -8550,112 +8490,112 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Contact streak: 10/29 over last 7 games</t>
+          <t>Last 7 games: 4/23, 1 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.8% barrel, 3.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.8% barrel, 15.8 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>37.48</t>
+          <t>35.37</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>86.41</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>98.4142</t>
+          <t>98.424</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.422</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1497</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3293</t>
+          <t>0.2688</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>69.41</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>32.98</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>33.73</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1641</t>
+          <t>0.126</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>88.83</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.3507</t>
+          <t>0.4213</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1116</t>
+          <t>0.1598</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>28.63</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -8681,12 +8621,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -8711,7 +8651,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -8730,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8744,11 +8684,11 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>41</v>
+        <v>31.3</v>
       </c>
       <c r="Q11" t="n">
         <v>22.3</v>
@@ -8757,13 +8697,13 @@
         <v>45.6</v>
       </c>
       <c r="S11" t="n">
-        <v>94.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T11" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U11" t="n">
-        <v>50.3</v>
+        <v>52.1</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -8777,7 +8717,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -8815,12 +8755,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -8830,12 +8770,12 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Contact streak: 7/21 over last 7 games</t>
+          <t>Contact streak: 10/29 over last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.8% barrel, 3.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.8% barrel, 3.8 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -8845,67 +8785,67 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>37.48</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>90.06</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>100.2939</t>
+          <t>98.4142</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4775</t>
+          <t>0.422</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1888</t>
+          <t>0.1497</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3668</t>
+          <t>0.3293</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>70.08</t>
+          <t>69.46</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>36.05</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>27.63</t>
+          <t>33.73</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1734</t>
+          <t>0.1641</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -8961,24 +8901,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>660688</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Keibert Ruiz</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>WSH</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-09-07T02:10:00Z</t>
@@ -8991,17 +8931,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Justin Wrobleski</t>
+          <t>Andrew Alvarez</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>680736</t>
+          <t>674841</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -9010,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>42.9</v>
+        <v>46</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -9024,62 +8964,58 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>16.1</v>
+        <v>41</v>
       </c>
       <c r="Q12" t="n">
-        <v>45.5</v>
+        <v>22.3</v>
       </c>
       <c r="R12" t="n">
         <v>45.6</v>
       </c>
       <c r="S12" t="n">
-        <v>71.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>61.7</v>
+        <v>50.3</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9099,12 +9035,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -9114,12 +9050,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Contact streak: 9/22 over last 7 games</t>
+          <t>Contact streak: 7/21 over last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.8% barrel, 15.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.8% barrel, 3.8 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -9129,97 +9065,97 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>35.24</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>90.06</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>97.6371</t>
+          <t>100.2939</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3622</t>
+          <t>0.4775</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1087</t>
+          <t>0.1888</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.2863</t>
+          <t>0.3668</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>67.22</t>
+          <t>70.08</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>55.59</t>
+          <t>36.05</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>27.63</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1396</t>
+          <t>0.1734</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>39.82</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>88.83</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.4213</t>
+          <t>0.3507</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1598</t>
+          <t>0.1116</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>28.63</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -9854,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>39.1</v>
+        <v>39.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9868,7 +9804,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -9881,7 +9817,7 @@
         <v>45.6</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
         <v>78</v>
@@ -9891,39 +9827,35 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10934,7 +10866,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nasim Nunez</t>
+          <t>Nasim Nuñez</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -10978,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>32</v>
+        <v>32.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10992,7 +10924,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -11005,7 +10937,7 @@
         <v>45.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -11015,39 +10947,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
